--- a/למילוי דוח מיניפ.xlsx
+++ b/למילוי דוח מיניפ.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\מסמכים\מבחר שנה ב\מיני פרויקט\dotNet5786_3997_6339\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A90A664-778B-43BA-AD82-00E222B14599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335B9454-EACB-4221-B23B-128B0CCCD82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34710" yWindow="2985" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
   <si>
     <t>תוספת</t>
   </si>
@@ -226,6 +226,9 @@
   </si>
   <si>
     <t>כמובן רק אם ניתן למחוק את השליח ניתן ללחוץ עליו  מופעל ע"י פונקציית  commands</t>
+  </si>
+  <si>
+    <t>קיים   בקובץ DalList DalXml</t>
   </si>
 </sst>
 </file>
@@ -401,13 +404,13 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -701,7 +704,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
@@ -710,7 +713,7 @@
       <c r="C1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>58</v>
       </c>
       <c r="I1" t="s">
@@ -718,14 +721,14 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="A2" s="10"/>
+      <c r="A2" s="11"/>
       <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -746,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -768,7 +771,7 @@
       <c r="D5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="11"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">

--- a/למילוי דוח מיניפ.xlsx
+++ b/למילוי דוח מיניפ.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\david\מסמכים\מבחר שנה ב\מיני פרויקט\dotNet5786_3997_6339\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\מכון לב\מיני פרוייקט\dotNet5786_3997_6339\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335B9454-EACB-4221-B23B-128B0CCCD82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85611832-138C-4559-9A32-AFA5B5AE7998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34710" yWindow="2985" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="גיליון1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
   <si>
     <t>תוספת</t>
   </si>
@@ -229,6 +229,12 @@
   </si>
   <si>
     <t>קיים   בקובץ DalList DalXml</t>
+  </si>
+  <si>
+    <t>המערכת מאוד מהירה</t>
+  </si>
+  <si>
+    <t>רק הזמנות שבאמצע משלוח</t>
   </si>
 </sst>
 </file>
@@ -695,15 +701,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
     <col min="2" max="2" width="37.5" customWidth="1"/>
     <col min="3" max="3" width="19.75" customWidth="1"/>
     <col min="4" max="4" width="4.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -720,7 +726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="7" t="s">
         <v>2</v>
@@ -730,7 +736,7 @@
       </c>
       <c r="D2" s="11"/>
     </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -744,7 +750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -758,7 +764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -768,12 +774,12 @@
       <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>58</v>
+      <c r="D5" s="1">
+        <v>1</v>
       </c>
       <c r="G5" s="9"/>
     </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -787,7 +793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="70" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>25</v>
       </c>
@@ -804,7 +810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
@@ -818,7 +824,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -832,7 +838,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
@@ -846,7 +852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -860,7 +866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
@@ -874,7 +880,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -888,7 +894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>36</v>
       </c>
@@ -902,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="45" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="42" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>37</v>
       </c>
@@ -916,7 +922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
@@ -930,7 +936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>40</v>
       </c>
@@ -944,7 +950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>13</v>
       </c>
@@ -958,7 +964,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
@@ -972,7 +978,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
@@ -986,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="56" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>46</v>
       </c>
@@ -1000,7 +1006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1014,7 +1020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="56" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>17</v>
       </c>
@@ -1028,7 +1034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1042,7 +1048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1056,7 +1062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>20</v>
       </c>
@@ -1070,11 +1076,13 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="C27" s="1" t="s">
         <v>7</v>
       </c>
@@ -1082,17 +1090,19 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="60" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="56" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>51</v>
       </c>
@@ -1104,7 +1114,7 @@
       </c>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" ht="105" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>53</v>
       </c>
@@ -1116,7 +1126,7 @@
       </c>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>55</v>
       </c>
@@ -1128,7 +1138,7 @@
       </c>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" ht="45" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>49</v>
       </c>

--- a/למילוי דוח מיניפ.xlsx
+++ b/למילוי דוח מיניפ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\מכון לב\מיני פרוייקט\dotNet5786_3997_6339\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85611832-138C-4559-9A32-AFA5B5AE7998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4CBCAA-6C9D-4110-87EA-FD53406D9366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="72">
   <si>
     <t>תוספת</t>
   </si>
@@ -225,9 +225,6 @@
     <t>רק בעת כניסה למערכת. ממסך הניהול ניתן רק לשנות ללא צפיה. ממסך השליח ניתן גם לראות את הקוד הקיים.</t>
   </si>
   <si>
-    <t>כמובן רק אם ניתן למחוק את השליח ניתן ללחוץ עליו  מופעל ע"י פונקציית  commands</t>
-  </si>
-  <si>
     <t>קיים   בקובץ DalList DalXml</t>
   </si>
   <si>
@@ -235,6 +232,15 @@
   </si>
   <si>
     <t>רק הזמנות שבאמצע משלוח</t>
+  </si>
+  <si>
+    <t xml:space="preserve">הוספת גלגל מסתובב </t>
+  </si>
+  <si>
+    <t>מסך שליח אם יש הזמנות</t>
+  </si>
+  <si>
+    <t xml:space="preserve">כמובן רק אם ניתן למחוק את השליח ניתן ללחוץ עליו </t>
   </si>
 </sst>
 </file>
@@ -303,7 +309,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -379,12 +385,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
@@ -417,6 +434,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -700,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" customWidth="1"/>
@@ -755,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -1053,7 +1073,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -1081,7 +1101,7 @@
         <v>59</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>7</v>
@@ -1095,12 +1115,14 @@
         <v>21</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -1112,7 +1134,9 @@
       <c r="C29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
@@ -1124,7 +1148,9 @@
       <c r="C30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="31" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
@@ -1136,7 +1162,9 @@
       <c r="C31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -1148,7 +1176,23 @@
       <c r="C32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/למילוי דוח מיניפ.xlsx
+++ b/למילוי דוח מיניפ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\מכון לב\מיני פרוייקט\dotNet5786_3997_6339\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4CBCAA-6C9D-4110-87EA-FD53406D9366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A47422D9-7676-458F-99A4-4EAA23E5F78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/למילוי דוח מיניפ.xlsx
+++ b/למילוי דוח מיניפ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\מכון לב\מיני פרוייקט\dotNet5786_3997_6339\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A47422D9-7676-458F-99A4-4EAA23E5F78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5913A331-F306-4B7F-BB48-D877EF59C249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,9 +144,6 @@
     <t xml:space="preserve">לדוגמא במסך הגדרות מנהל על ידי קריאה ל PL.Tools.OnNumericOnly </t>
   </si>
   <si>
-    <t xml:space="preserve">שימוש לגבי צבע כפתור כשעומדים עליו PL.App.xaml </t>
-  </si>
-  <si>
     <t xml:space="preserve">לחיצה על אנטר </t>
   </si>
   <si>
@@ -241,6 +238,9 @@
   </si>
   <si>
     <t xml:space="preserve">כמובן רק אם ניתן למחוק את השליח ניתן ללחוץ עליו </t>
+  </si>
+  <si>
+    <t>שימוש לגבי צבע כפתור כשעומדים עליו PL.App.xaml לדוגמא בכפתור מחק שליח.</t>
   </si>
 </sst>
 </file>
@@ -740,7 +740,7 @@
         <v>3</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -775,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -789,7 +789,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>28</v>
@@ -900,12 +900,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
@@ -933,7 +933,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
@@ -947,7 +947,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>7</v>
@@ -958,10 +958,10 @@
     </row>
     <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>7</v>
@@ -975,7 +975,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>7</v>
@@ -989,7 +989,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>7</v>
@@ -1003,7 +1003,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>7</v>
@@ -1014,10 +1014,10 @@
     </row>
     <row r="21" spans="1:4" ht="56" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>7</v>
@@ -1031,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>7</v>
@@ -1045,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -1059,7 +1059,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>7</v>
@@ -1073,7 +1073,7 @@
         <v>19</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -1087,7 +1087,7 @@
         <v>20</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>7</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="27" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>7</v>
@@ -1115,7 +1115,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>28</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="29" spans="1:4" ht="28" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>28</v>
@@ -1140,10 +1140,10 @@
     </row>
     <row r="30" spans="1:4" ht="84" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>28</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="31" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>28</v>
@@ -1168,10 +1168,10 @@
     </row>
     <row r="32" spans="1:4" ht="42" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>28</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>70</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>7</v>
